--- a/output/20260630_fix_owner_new_import/payment_price_manual_review_examples_25_after_rules_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/payment_price_manual_review_examples_25_after_rules_20260630.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="manual_review_30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'manual_review_30'!$A$1:$X$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'manual_review_30'!$A$1:$Y$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -508,100 +508,105 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>contract_id</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>client_fio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>contract_name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>card</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>duration_type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>create_date</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>payment_date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>activation_date</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>freeze</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>guests</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>visits_left</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>amount_of_payments</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>payment_left</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>type_of_payment</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>manager</t>
         </is>
@@ -616,74 +621,70 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>00000114628</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>000059966</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>+7 (964) 3092913</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Бессмертная Анна Сергеевна</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Абонемент Неделя Фитнес</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>8211111115510</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023-09-13</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>2023-09-13</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>2023-09-13</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>2023-09-19</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr"/>
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -694,8 +695,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
@@ -710,74 +716,70 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>00000118100</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>000061762</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>+7 (921) 0146472</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Матросов Сергей Валерьевич</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Абонемент Неделя Фитнес</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>1111111143353</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>2024-01-02</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>2024-01-02</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>2024-01-02</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>2024-01-08</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr"/>
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -788,8 +790,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
         </is>
@@ -804,74 +811,70 @@
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>00000108008</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>000044882</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>+7 (953) 7562189, +7 (993) 3831088</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Власова Юлия Александровна</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Абонемент Неделя сайт 2023</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>1329000090248</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>2021-03-12</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>2023-02-18</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>2023-02-18</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr"/>
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -882,8 +885,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
@@ -898,74 +906,70 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>00000100577</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>000024568</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>+7 (911) 4372967</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Чуркина Виктория Сергеевна</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>СУБАРЕНДА безлимит</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>000040084374</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>2022-06-28</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>2022-07-31</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="inlineStr"/>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -976,8 +980,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
@@ -992,78 +1001,74 @@
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>00000055624</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>000023705</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>+7 (921) 7003199</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Детчуева Елена Павловна</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>8811111112788</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>2019-02-28</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>2019-02-28</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>2019-02-28</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>2020-07-17</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1074,8 +1079,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
@@ -1090,74 +1100,70 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>00000041638</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>000004608</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>+7 (964) 3171819</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Девяткина Анастасия Сергеевна</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>0000400191780</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>2020-02-26</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="inlineStr"/>
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1168,8 +1174,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
@@ -1184,74 +1195,70 @@
       <c r="B8" s="3" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>00000113569</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>000058839</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>+7 (921) 0146295</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Карпов Вадим Александрович</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Абонемент Неделя Фитнес</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>1111111142677</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>2023-07-10</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>2023-08-20</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr"/>
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1262,8 +1269,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
@@ -1278,74 +1290,70 @@
       <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>00000107036</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>000056054</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>+7 (960) 2139886</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Боярова Галина Федоровна</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Абонемент Неделя сайт 2023</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>1111111123805</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>2023-01-24</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>2023-03-01</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr"/>
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1356,8 +1364,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
@@ -1374,72 +1387,72 @@
       <c r="D10" s="3" t="inlineStr"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>отказники</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>00000098029</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>000013059</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>+7 (911) 4069842</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Острая Ирина Владимировна (Тренер)</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>СУБАРЕНДА безлимит</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>1150000405332</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>2020-03-04</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1450,8 +1463,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>Седунова Анна Сергеевна</t>
         </is>
@@ -1466,74 +1484,70 @@
       <c r="B11" s="3" t="inlineStr"/>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>00000139318</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>000069754</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>+7 (953) 5287037</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Ермакова Елена Александровна</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>115000230712</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>2025-08-23</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>2025-08-23</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>2025-08-23</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr"/>
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1546,10 +1560,15 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>Васьковская Виктория Петровна</t>
         </is>
@@ -1564,74 +1583,70 @@
       <c r="B12" s="3" t="inlineStr"/>
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>00000115336</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>000056821</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>+7 (993) 7600319</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>Элатруш Юссеф Мустафа Мохамед</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>115000184817</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>2023-10-09</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>2023-10-09</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>2023-10-09</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="inlineStr"/>
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1644,10 +1659,15 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
@@ -1662,74 +1682,70 @@
       <c r="B13" s="3" t="inlineStr"/>
       <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>00000148373</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>000073172</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>+7 (905) 2580016</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Отаджанов Мансурбек Кодирберди Угли</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев СПЕЦПРЕДЛОЖЕНИЕ</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>8821111120737</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>2027-06-20</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1742,10 +1758,15 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
@@ -1760,90 +1781,91 @@
       <c r="B14" s="3" t="inlineStr"/>
       <c r="C14" s="3" t="inlineStr"/>
       <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>00000041707</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>000023743</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>+7 (960) 2195248, +7 (8142) 774418</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>Пателина Александра Владимировна</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>115000465428</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>2019-02-04</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>2019-02-04</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>2019-02-04</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>2020-02-03</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr"/>
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>5999</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="V14" s="3" t="inlineStr">
         <is>
           <t>5999</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
@@ -1858,90 +1880,91 @@
       <c r="B15" s="3" t="inlineStr"/>
       <c r="C15" s="3" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>00000041704</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>000023763</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>+7 (911) 6650686</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Фромертене Екатерина Викторовна</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>0000400265658</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>2019-01-19</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>2019-02-19</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>2020-02-18</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr"/>
       <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>7249</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t>7249</t>
         </is>
       </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
@@ -1956,90 +1979,91 @@
       <c r="B16" s="3" t="inlineStr"/>
       <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>00000150603</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>000009536</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>+7 (921) 6274391</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>Куфтарева Зоя Викторовна</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев + подарок (СПЕЦПРЕДЛОЖЕНИЕ)</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>2027-05-22</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>11990</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
+      <c r="V16" s="3" t="inlineStr">
         <is>
           <t>11990</t>
         </is>
       </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="X16" s="3" t="inlineStr">
+      <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
         </is>
@@ -2054,90 +2078,91 @@
       <c r="B17" s="3" t="inlineStr"/>
       <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>00000041564</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>000006325</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>+7 (911) 4291017</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Иванкович Наталья Петровна</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 1 МЕСЯЦ БЕЗЛИМИТ</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>1150003341828</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>2019-02-25</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>2019-02-25</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>2019-03-24</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr"/>
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr">
+      <c r="V17" s="3" t="inlineStr">
         <is>
           <t>2800</t>
         </is>
       </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="X17" s="3" t="inlineStr">
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
@@ -2152,74 +2177,70 @@
       <c r="B18" s="3" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>00000041546</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>000023699</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>+7 (911) 0528656</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Путкова Елизавета Алексеевна</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ САЙТ</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>000040035581</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>2019-02-27</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>2019-03-06</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr"/>
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -2230,8 +2251,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
@@ -2248,72 +2274,72 @@
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t>отказники</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
           <t>00000098600</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>000044469</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>+7 (981) 4019377</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Кодиров Салимбек Хуршедович</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ ФИТНЕСА БЕСПЛАТНО</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>1329000081703</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>2021-02-27</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>2022-04-18</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>2022-04-18</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>2022-04-24</t>
         </is>
       </c>
-      <c r="Q19" s="3" t="inlineStr"/>
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -2324,8 +2350,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr"/>
+      <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
@@ -2340,74 +2371,70 @@
       <c r="B20" s="3" t="inlineStr"/>
       <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>00000067639</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>000021021</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>+7 (985) 8833916</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Баландина Екатерина Алексеевна</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Абонемент МУЛЬТИКАРТА 12 месяцев</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>2010-03-05</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>2010-03-05</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>2021-05-25</t>
         </is>
       </c>
-      <c r="Q20" s="3" t="inlineStr"/>
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -2418,8 +2445,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr">
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr"/>
+      <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
         </is>
@@ -2434,74 +2466,70 @@
       <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>00000038233</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>000013907</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>+7 (921) 7261616</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>Плугарев Владимир Иванович</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>1150002229080</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>2020-10-26</t>
         </is>
       </c>
-      <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -2512,8 +2540,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr">
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr"/>
+      <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
@@ -2528,74 +2561,70 @@
       <c r="B22" s="3" t="inlineStr"/>
       <c r="C22" s="3" t="inlineStr"/>
       <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>00000043326</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>000010687</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>+7 (981) 4033028</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Максимова Елена Владимировна</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ ДРУГ</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>1150004046630</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>2019-05-06</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>2019-05-06</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t>2019-05-06</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>2019-05-13</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="inlineStr"/>
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -2606,8 +2635,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr"/>
+      <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
         </is>
@@ -2622,74 +2656,70 @@
       <c r="B23" s="3" t="inlineStr"/>
       <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>00000099287</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>000017139</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>+7 (911) 4016289</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Петугина (Степанова) Майя Александровна</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Абонемент 10 ДНЕЙ</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>1329000079168</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>2022-05-10</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>2022-05-10</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
+      <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>2022-05-20</t>
         </is>
       </c>
-      <c r="Q23" s="3" t="inlineStr"/>
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -2700,8 +2730,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr">
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr"/>
+      <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
         </is>
@@ -2716,90 +2751,91 @@
       <c r="B24" s="3" t="inlineStr"/>
       <c r="C24" s="3" t="inlineStr"/>
       <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>00000043166</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>000013446</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>+7 (911) 6687253, +7 (921) 8042001</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>Пашук Алена Евгеньевна</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="O24" s="3" t="inlineStr">
         <is>
           <t>2019-04-27</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="P24" s="3" t="inlineStr">
         <is>
           <t>2019-04-27</t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr">
+      <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>2020-07-17</t>
         </is>
       </c>
-      <c r="Q24" s="3" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr"/>
       <c r="S24" s="3" t="inlineStr"/>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>6599</t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr">
+      <c r="V24" s="3" t="inlineStr">
         <is>
           <t>6599</t>
         </is>
       </c>
-      <c r="V24" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
           <t>безналичные</t>
         </is>
       </c>
-      <c r="X24" s="3" t="inlineStr">
+      <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
         </is>
@@ -2814,90 +2850,91 @@
       <c r="B25" s="3" t="inlineStr"/>
       <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>00000062156</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>000020780</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>+7 (953) 5252014</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Якушенков Александр Сергеевич</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Абонемент УЛЬТРА 12 месяцев</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>115000265233</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="O25" s="3" t="inlineStr">
         <is>
           <t>2019-01-15</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>2019-01-15</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr">
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>2021-07-06</t>
         </is>
       </c>
-      <c r="Q25" s="3" t="inlineStr"/>
       <c r="R25" s="3" t="inlineStr"/>
       <c r="S25" s="3" t="inlineStr"/>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
         <is>
           <t>6499</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr">
+      <c r="V25" s="3" t="inlineStr">
         <is>
           <t>6499</t>
         </is>
       </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="X25" s="3" t="inlineStr">
+      <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>Лисовская Екатерина Александровна</t>
         </is>
@@ -2912,97 +2949,98 @@
       <c r="B26" s="3" t="inlineStr"/>
       <c r="C26" s="3" t="inlineStr"/>
       <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>00000074249</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>000025519</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>+7 (921) 8000849</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>Койбин Игорь Анатольевич</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>Абонемент НЕДЕЛЯ САЙТ</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>115000205130</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
           <t>месяц</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>2020-10-09</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>2020-10-09</t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
+      <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>2020-10-16</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="inlineStr"/>
       <c r="R26" s="3" t="inlineStr"/>
       <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
+      <c r="V26" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
           <t>наличные</t>
         </is>
       </c>
-      <c r="X26" s="3" t="inlineStr">
+      <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X26"/>
+  <autoFilter ref="A1:Y26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>